--- a/outputs/bond_results_with_Tier_2_type_VBMA_Bond_FI.xlsx
+++ b/outputs/bond_results_with_Tier_2_type_VBMA_Bond_FI.xlsx
@@ -1,40 +1,105 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="18">
+  <si>
+    <t>bond_id</t>
+  </si>
+  <si>
+    <t>full_price</t>
+  </si>
+  <si>
+    <t>straight_price</t>
+  </si>
+  <si>
+    <t>diff</t>
+  </si>
+  <si>
+    <t>shock</t>
+  </si>
+  <si>
+    <t>VCB_BOND_RL15_2017_7</t>
+  </si>
+  <si>
+    <t>VCB_BOND_RL15_2017_12</t>
+  </si>
+  <si>
+    <t>VCBH2131003</t>
+  </si>
+  <si>
+    <t>VCB12604</t>
+  </si>
+  <si>
+    <t>HDBC8Y253302 (HDB125025)</t>
+  </si>
+  <si>
+    <t>Test_Floor_American</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,85 +107,36 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -408,189 +424,742 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E43"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>bond_id</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>full_price</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>straight_price</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>diff</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>shock</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Test_Floor_American</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>91.89418153510748</v>
-      </c>
-      <c r="C2" t="n">
-        <v>93.03866493403159</v>
-      </c>
-      <c r="D2" t="n">
-        <v>-1.144483398924109</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Test_Floor_American</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>90.16810556011667</v>
-      </c>
-      <c r="C3" t="n">
-        <v>90.85797655922802</v>
-      </c>
-      <c r="D3" t="n">
-        <v>-0.6898709991113492</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Test_Floor_American</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>92.03822506446784</v>
-      </c>
-      <c r="C4" t="n">
-        <v>97.70178351185658</v>
-      </c>
-      <c r="D4" t="n">
-        <v>-5.663558447388738</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Test_Floor_American</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>87.0200956301352</v>
-      </c>
-      <c r="C5" t="n">
-        <v>89.22642390915161</v>
-      </c>
-      <c r="D5" t="n">
-        <v>-2.206328279016404</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Test_Floor_American</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>90.95779044191957</v>
-      </c>
-      <c r="C6" t="n">
-        <v>99.19699897507843</v>
-      </c>
-      <c r="D6" t="n">
-        <v>-8.239208533158859</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Test_Floor_American</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>89.41023419372532</v>
-      </c>
-      <c r="C7" t="n">
-        <v>98.65523003807843</v>
-      </c>
-      <c r="D7" t="n">
-        <v>-9.244995844353113</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Test_Floor_American</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>83.15270259775983</v>
-      </c>
-      <c r="C8" t="n">
-        <v>94.68821788906425</v>
-      </c>
-      <c r="D8" t="n">
-        <v>-11.53551529130442</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2">
+        <v>100.2928628528856</v>
+      </c>
+      <c r="C2">
+        <v>101.4185344484734</v>
+      </c>
+      <c r="D2">
+        <v>-1.125671595587789</v>
+      </c>
+      <c r="E2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3">
+        <v>83.23958089141689</v>
+      </c>
+      <c r="C3">
+        <v>83.24282324369602</v>
+      </c>
+      <c r="D3">
+        <v>-0.0032423522791305</v>
+      </c>
+      <c r="E3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4">
+        <v>108.6510210680242</v>
+      </c>
+      <c r="C4">
+        <v>124.478721541857</v>
+      </c>
+      <c r="D4">
+        <v>-15.82770047383276</v>
+      </c>
+      <c r="E4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>96.27640057991957</v>
+      </c>
+      <c r="C5">
+        <v>96.43001296514238</v>
+      </c>
+      <c r="D5">
+        <v>-0.1536123852228144</v>
+      </c>
+      <c r="E5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>98.72061589332071</v>
+      </c>
+      <c r="C6">
+        <v>102.616417125411</v>
+      </c>
+      <c r="D6">
+        <v>-3.895801232090264</v>
+      </c>
+      <c r="E6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <v>94.22628174266742</v>
+      </c>
+      <c r="C7">
+        <v>95.28510818544144</v>
+      </c>
+      <c r="D7">
+        <v>-1.05882644277402</v>
+      </c>
+      <c r="E7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8">
+        <v>105.6357174042539</v>
+      </c>
+      <c r="C8">
+        <v>107.9633183787595</v>
+      </c>
+      <c r="D8">
+        <v>-2.327600974505586</v>
+      </c>
+      <c r="E8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9">
+        <v>99.14695998323009</v>
+      </c>
+      <c r="C9">
+        <v>100.2813460321808</v>
+      </c>
+      <c r="D9">
+        <v>-1.134386048950745</v>
+      </c>
+      <c r="E9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10">
+        <v>81.84860928044264</v>
+      </c>
+      <c r="C10">
+        <v>81.85231980665345</v>
+      </c>
+      <c r="D10">
+        <v>-0.003710526210809917</v>
+      </c>
+      <c r="E10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" t="s">
+        <v>6</v>
+      </c>
+      <c r="B11">
+        <v>108.0468118342754</v>
+      </c>
+      <c r="C11">
+        <v>123.7796884896156</v>
+      </c>
+      <c r="D11">
+        <v>-15.73287665534018</v>
+      </c>
+      <c r="E11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B12">
+        <v>94.88208515588973</v>
+      </c>
+      <c r="C12">
+        <v>95.02884575702636</v>
+      </c>
+      <c r="D12">
+        <v>-0.1467606011366342</v>
+      </c>
+      <c r="E12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" t="s">
+        <v>6</v>
+      </c>
+      <c r="B13">
+        <v>97.59613855516017</v>
+      </c>
+      <c r="C13">
+        <v>101.7092322303785</v>
+      </c>
+      <c r="D13">
+        <v>-4.113093675218309</v>
+      </c>
+      <c r="E13" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" t="s">
+        <v>6</v>
+      </c>
+      <c r="B14">
+        <v>93.06497357280486</v>
+      </c>
+      <c r="C14">
+        <v>94.22862317281319</v>
+      </c>
+      <c r="D14">
+        <v>-1.163649600008327</v>
+      </c>
+      <c r="E14" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" t="s">
+        <v>6</v>
+      </c>
+      <c r="B15">
+        <v>104.555704311265</v>
+      </c>
+      <c r="C15">
+        <v>106.7358441292879</v>
+      </c>
+      <c r="D15">
+        <v>-2.180139818022951</v>
+      </c>
+      <c r="E15" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" t="s">
+        <v>7</v>
+      </c>
+      <c r="B16">
+        <v>94.45130500536031</v>
+      </c>
+      <c r="C16">
+        <v>94.48018495458813</v>
+      </c>
+      <c r="D16">
+        <v>-0.02887994922781445</v>
+      </c>
+      <c r="E16" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" t="s">
+        <v>7</v>
+      </c>
+      <c r="B17">
+        <v>79.0749567194476</v>
+      </c>
+      <c r="C17">
+        <v>79.07495675810853</v>
+      </c>
+      <c r="D17">
+        <v>-3.866092868065607E-08</v>
+      </c>
+      <c r="E17" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" t="s">
+        <v>7</v>
+      </c>
+      <c r="B18">
+        <v>103.7370433910556</v>
+      </c>
+      <c r="C18">
+        <v>113.3734615546756</v>
+      </c>
+      <c r="D18">
+        <v>-9.636418163619979</v>
+      </c>
+      <c r="E18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" t="s">
+        <v>7</v>
+      </c>
+      <c r="B19">
+        <v>91.31332344085921</v>
+      </c>
+      <c r="C19">
+        <v>91.31672187623788</v>
+      </c>
+      <c r="D19">
+        <v>-0.003398435378670683</v>
+      </c>
+      <c r="E19" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" t="s">
+        <v>7</v>
+      </c>
+      <c r="B20">
+        <v>94.12490151402318</v>
+      </c>
+      <c r="C20">
+        <v>94.35661890141539</v>
+      </c>
+      <c r="D20">
+        <v>-0.2317173873922087</v>
+      </c>
+      <c r="E20" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" t="s">
+        <v>7</v>
+      </c>
+      <c r="B21">
+        <v>88.38881176841713</v>
+      </c>
+      <c r="C21">
+        <v>88.39659947327915</v>
+      </c>
+      <c r="D21">
+        <v>-0.00778770486202518</v>
+      </c>
+      <c r="E21" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" t="s">
+        <v>7</v>
+      </c>
+      <c r="B22">
+        <v>100.3228616697578</v>
+      </c>
+      <c r="C22">
+        <v>100.9977555262105</v>
+      </c>
+      <c r="D22">
+        <v>-0.6748938564526981</v>
+      </c>
+      <c r="E22" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23">
+        <v>90.40953266487887</v>
+      </c>
+      <c r="C23">
+        <v>90.57501894336782</v>
+      </c>
+      <c r="D23">
+        <v>-0.1654862784889559</v>
+      </c>
+      <c r="E23" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" t="s">
+        <v>8</v>
+      </c>
+      <c r="B24">
+        <v>86.31243538421245</v>
+      </c>
+      <c r="C24">
+        <v>86.38078966755563</v>
+      </c>
+      <c r="D24">
+        <v>-0.06835428334318294</v>
+      </c>
+      <c r="E24" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" t="s">
+        <v>8</v>
+      </c>
+      <c r="B25">
+        <v>95.15965696204083</v>
+      </c>
+      <c r="C25">
+        <v>96.98330692565634</v>
+      </c>
+      <c r="D25">
+        <v>-1.823649963615509</v>
+      </c>
+      <c r="E25" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" t="s">
+        <v>8</v>
+      </c>
+      <c r="B26">
+        <v>86.9247836819839</v>
+      </c>
+      <c r="C26">
+        <v>87.00447130033307</v>
+      </c>
+      <c r="D26">
+        <v>-0.07968761834916904</v>
+      </c>
+      <c r="E26" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" t="s">
+        <v>8</v>
+      </c>
+      <c r="B27">
+        <v>92.6926140605142</v>
+      </c>
+      <c r="C27">
+        <v>93.8998900956033</v>
+      </c>
+      <c r="D27">
+        <v>-1.207276035089095</v>
+      </c>
+      <c r="E27" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" t="s">
+        <v>8</v>
+      </c>
+      <c r="B28">
+        <v>91.02060814015759</v>
+      </c>
+      <c r="C28">
+        <v>91.68996737179141</v>
+      </c>
+      <c r="D28">
+        <v>-0.6693592316338197</v>
+      </c>
+      <c r="E28" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" t="s">
+        <v>8</v>
+      </c>
+      <c r="B29">
+        <v>89.44064453147337</v>
+      </c>
+      <c r="C29">
+        <v>89.67651931353191</v>
+      </c>
+      <c r="D29">
+        <v>-0.235874782058545</v>
+      </c>
+      <c r="E29" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" t="s">
+        <v>9</v>
+      </c>
+      <c r="B30">
+        <v>103.8730328905378</v>
+      </c>
+      <c r="C30">
+        <v>93.72810581086661</v>
+      </c>
+      <c r="D30">
+        <v>10.14492707967122</v>
+      </c>
+      <c r="E30" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" t="s">
+        <v>9</v>
+      </c>
+      <c r="B31">
+        <v>104.0289670617306</v>
+      </c>
+      <c r="C31">
+        <v>91.68584929702509</v>
+      </c>
+      <c r="D31">
+        <v>12.34311776470554</v>
+      </c>
+      <c r="E31" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" t="s">
+        <v>9</v>
+      </c>
+      <c r="B32">
+        <v>103.8862560495781</v>
+      </c>
+      <c r="C32">
+        <v>97.49065178935693</v>
+      </c>
+      <c r="D32">
+        <v>6.395604260221205</v>
+      </c>
+      <c r="E32" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" t="s">
+        <v>9</v>
+      </c>
+      <c r="B33">
+        <v>102.6011791096449</v>
+      </c>
+      <c r="C33">
+        <v>87.28717302879417</v>
+      </c>
+      <c r="D33">
+        <v>15.31400608085073</v>
+      </c>
+      <c r="E33" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" t="s">
+        <v>9</v>
+      </c>
+      <c r="B34">
+        <v>105.292997713341</v>
+      </c>
+      <c r="C34">
+        <v>100.0712850017111</v>
+      </c>
+      <c r="D34">
+        <v>5.221712711629849</v>
+      </c>
+      <c r="E34" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" t="s">
+        <v>9</v>
+      </c>
+      <c r="B35">
+        <v>105.390905587024</v>
+      </c>
+      <c r="C35">
+        <v>97.79432739575361</v>
+      </c>
+      <c r="D35">
+        <v>7.59657819127041</v>
+      </c>
+      <c r="E35" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" t="s">
+        <v>9</v>
+      </c>
+      <c r="B36">
+        <v>102.3839846352367</v>
+      </c>
+      <c r="C36">
+        <v>89.69373707784041</v>
+      </c>
+      <c r="D36">
+        <v>12.69024755739632</v>
+      </c>
+      <c r="E36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" t="s">
+        <v>10</v>
+      </c>
+      <c r="B37">
+        <v>92.67950663692727</v>
+      </c>
+      <c r="C37">
+        <v>93.95419579128477</v>
+      </c>
+      <c r="D37">
+        <v>-1.274689154357503</v>
+      </c>
+      <c r="E37" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" t="s">
+        <v>10</v>
+      </c>
+      <c r="B38">
+        <v>90.89515672601779</v>
+      </c>
+      <c r="C38">
+        <v>91.65520354109026</v>
+      </c>
+      <c r="D38">
+        <v>-0.7600468150724708</v>
+      </c>
+      <c r="E38" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" t="s">
+        <v>10</v>
+      </c>
+      <c r="B39">
+        <v>93.7394109999353</v>
+      </c>
+      <c r="C39">
+        <v>98.43136367011913</v>
+      </c>
+      <c r="D39">
+        <v>-4.691952670183824</v>
+      </c>
+      <c r="E39" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" t="s">
+        <v>10</v>
+      </c>
+      <c r="B40">
+        <v>88.78055835042721</v>
+      </c>
+      <c r="C40">
+        <v>89.41254496603925</v>
+      </c>
+      <c r="D40">
+        <v>-0.6319866156120355</v>
+      </c>
+      <c r="E40" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" t="s">
+        <v>10</v>
+      </c>
+      <c r="B41">
+        <v>94.62420934804692</v>
+      </c>
+      <c r="C41">
+        <v>98.63455299222554</v>
+      </c>
+      <c r="D41">
+        <v>-4.010343644178619</v>
+      </c>
+      <c r="E41" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" t="s">
+        <v>10</v>
+      </c>
+      <c r="B42">
+        <v>94.14209679150193</v>
+      </c>
+      <c r="C42">
+        <v>97.06602665161765</v>
+      </c>
+      <c r="D42">
+        <v>-2.92392986011572</v>
+      </c>
+      <c r="E42" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" t="s">
+        <v>10</v>
+      </c>
+      <c r="B43">
+        <v>89.83003382429598</v>
+      </c>
+      <c r="C43">
+        <v>91.07694214520548</v>
+      </c>
+      <c r="D43">
+        <v>-1.246908320909498</v>
+      </c>
+      <c r="E43" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>